--- a/docs/AXI4-LITE TP.xlsx
+++ b/docs/AXI4-LITE TP.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vitacin-my.sharepoint.com/personal/akilan_k2022_vitstudent_ac_in/Documents/Desktop/Mirafra Details/SV/AXI4LITE_UVM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="192" documentId="8_{B39BE06C-7574-4CB7-9203-8159EAFEBEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C3CB491D-F7A9-45A2-B01B-BC49E1DA0DF9}"/>
+  <xr:revisionPtr revIDLastSave="280" documentId="8_{B39BE06C-7574-4CB7-9203-8159EAFEBEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9F21BFE2-CC61-47DD-A64B-ABD2FD71862A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{D2A6C99C-DFBF-474B-BD0C-9E2DDDBD48DF}"/>
+    <workbookView xWindow="2880" yWindow="1248" windowWidth="17280" windowHeight="10716" xr2:uid="{D2A6C99C-DFBF-474B-BD0C-9E2DDDBD48DF}"/>
   </bookViews>
   <sheets>
     <sheet name="TestPlan" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="133">
   <si>
     <t>Signal</t>
   </si>
@@ -314,9 +314,6 @@
     <t>Remarks</t>
   </si>
   <si>
-    <t>addr_handshake</t>
-  </si>
-  <si>
     <t>awvalid_stable</t>
   </si>
   <si>
@@ -329,9 +326,6 @@
     <t>When the AWVALID is asserted by master; it should remain stable until AWREADY is asserted by slave for transfer completion.</t>
   </si>
   <si>
-    <t>data_handshake</t>
-  </si>
-  <si>
     <t>wvalid_stable</t>
   </si>
   <si>
@@ -365,18 +359,9 @@
     <t>No. of Bins</t>
   </si>
   <si>
-    <t>AWADDR</t>
-  </si>
-  <si>
     <t>To verify the coverage of 32-bit address.</t>
   </si>
   <si>
-    <t>[0:24],[28:30],[34:38],[40:ff]</t>
-  </si>
-  <si>
-    <t>ARADDR</t>
-  </si>
-  <si>
     <t>WSTRB</t>
   </si>
   <si>
@@ -386,25 +371,70 @@
     <t>{1111},{0001},{1000},{0011},{1100},{0000}</t>
   </si>
   <si>
-    <t>BRESP</t>
-  </si>
-  <si>
-    <t>For okay,slverr,decerr</t>
-  </si>
-  <si>
-    <t>{00},{10},{11}</t>
-  </si>
-  <si>
-    <t>RRESP</t>
-  </si>
-  <si>
-    <t>{AWVALID,ARVALID}</t>
-  </si>
-  <si>
-    <t>For read,write,read/write.</t>
-  </si>
-  <si>
-    <t>{00},{01},{10},{11}</t>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>PARTIAL</t>
+  </si>
+  <si>
+    <t>AWADDR[5:2]</t>
+  </si>
+  <si>
+    <t>[0:9],[13:15]</t>
+  </si>
+  <si>
+    <t>ARADDR[5:2]</t>
+  </si>
+  <si>
+    <t>[0:12],15</t>
+  </si>
+  <si>
+    <t>WDATA</t>
+  </si>
+  <si>
+    <t>To check for possible data coverage.</t>
+  </si>
+  <si>
+    <t>low:[0:32'h0FFFF]</t>
+  </si>
+  <si>
+    <t>med:[32'h010000:32'H7FFFFFFF</t>
+  </si>
+  <si>
+    <t>high:[32'h:80000000:32'Hffffffff</t>
+  </si>
+  <si>
+    <t>Cross:{WDATA,WSTRB}</t>
+  </si>
+  <si>
+    <t>To cross-cover data and strobe</t>
+  </si>
+  <si>
+    <t>All possible values in range.</t>
+  </si>
+  <si>
+    <t>write-addr_handshake</t>
+  </si>
+  <si>
+    <t>write-data_handshake</t>
+  </si>
+  <si>
+    <t>read-addr_handshake</t>
+  </si>
+  <si>
+    <t>arvalid_stable</t>
+  </si>
+  <si>
+    <t>When the ARVALID is asserted by master; it should remain stable until ARREADY is asserted by slave for transfer completion.</t>
+  </si>
+  <si>
+    <t>read-data_handshake</t>
+  </si>
+  <si>
+    <t>rvalid_stable</t>
+  </si>
+  <si>
+    <t>When the RVALID is asserted by master; it should remain stable until RREADY is asserted by slave for transfer completion.</t>
   </si>
 </sst>
 </file>
@@ -469,17 +499,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1173,6 +1204,9 @@
       <c r="C26" t="s">
         <v>63</v>
       </c>
+      <c r="D26" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27">
@@ -1184,6 +1218,9 @@
       <c r="C27" t="s">
         <v>65</v>
       </c>
+      <c r="D27" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28">
@@ -1195,6 +1232,9 @@
       <c r="C28" t="s">
         <v>67</v>
       </c>
+      <c r="D28" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29">
@@ -1206,6 +1246,9 @@
       <c r="C29" t="s">
         <v>69</v>
       </c>
+      <c r="D29" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30">
@@ -1217,6 +1260,9 @@
       <c r="C30" t="s">
         <v>71</v>
       </c>
+      <c r="D30" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31">
@@ -1228,6 +1274,9 @@
       <c r="C31" t="s">
         <v>73</v>
       </c>
+      <c r="D31" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32">
@@ -1239,8 +1288,11 @@
       <c r="C32" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D32" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>8</v>
       </c>
@@ -1250,8 +1302,11 @@
       <c r="C33" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D33" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>9</v>
       </c>
@@ -1261,8 +1316,11 @@
       <c r="C34" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="D34" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>10</v>
       </c>
@@ -1271,6 +1329,9 @@
       </c>
       <c r="C35" t="s">
         <v>81</v>
+      </c>
+      <c r="D35" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1280,7 +1341,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB4A6954-B912-48D7-AF66-8BA14A397564}">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="17.44140625" customWidth="1"/>
@@ -1291,20 +1352,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>105</v>
+      <c r="A1" s="3" t="s">
+        <v>103</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>90</v>
@@ -1315,90 +1376,115 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2">
+        <v>13</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D4" t="s">
+        <v>116</v>
+      </c>
+      <c r="E4">
+        <v>14</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" t="s">
         <v>109</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D6" t="s">
         <v>110</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E6">
+        <v>6</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E2">
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B3" t="s">
-        <v>112</v>
-      </c>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5" t="s">
+      <c r="B8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>120</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>121</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C5" t="s">
-        <v>114</v>
-      </c>
-      <c r="D5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E5">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>3</v>
-      </c>
-      <c r="B7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D7" t="s">
-        <v>118</v>
-      </c>
-      <c r="E7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
-        <v>119</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="E8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>4</v>
-      </c>
-      <c r="B10" t="s">
-        <v>120</v>
-      </c>
-      <c r="C10" t="s">
-        <v>121</v>
-      </c>
-      <c r="D10" t="s">
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
         <v>122</v>
       </c>
-      <c r="E10">
-        <v>4</v>
+      <c r="C12" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" t="s">
+        <v>124</v>
+      </c>
+      <c r="E12">
+        <v>18</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1408,7 +1494,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{823E3F6F-D0F2-471C-97D0-6490AD26377C}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.77734375" customWidth="1"/>
@@ -1426,7 +1512,7 @@
       <c r="B1" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>86</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -1450,19 +1536,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C2" t="s">
         <v>92</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2" t="s">
         <v>93</v>
       </c>
-      <c r="D2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>94</v>
-      </c>
-      <c r="F2" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -1470,19 +1556,19 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" t="s">
         <v>97</v>
       </c>
-      <c r="C4" t="s">
+      <c r="E4" t="s">
         <v>98</v>
       </c>
-      <c r="D4" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" t="s">
-        <v>100</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>95</v>
+      <c r="F4" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -1490,19 +1576,50 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8" t="s">
+        <v>130</v>
+      </c>
+      <c r="C8" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" t="s">
         <v>101</v>
       </c>
-      <c r="C6" t="s">
+      <c r="E10" t="s">
         <v>102</v>
       </c>
-      <c r="D6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E6" t="s">
-        <v>104</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>95</v>
+      <c r="F10" t="s">
+        <v>94</v>
+      </c>
+      <c r="G10" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
